--- a/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
+++ b/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="13545" windowHeight="2310"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="17850" windowHeight="5940"/>
   </bookViews>
   <sheets>
     <sheet name="ProductSheet" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Item</t>
   </si>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t>Estimated  Value(RM)</t>
+  </si>
+  <si>
+    <t>Specification</t>
+  </si>
+  <si>
+    <t>Answer</t>
   </si>
 </sst>
 </file>
@@ -396,29 +402,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>9</v>
@@ -427,13 +431,7 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
+++ b/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="17850" windowHeight="5940"/>
+    <workbookView visibility="veryHidden" xWindow="0" yWindow="0" windowWidth="13545" windowHeight="4500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ProductSheet" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>Item</t>
   </si>
@@ -27,12 +27,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Unit Price (RM)</t>
-  </si>
-  <si>
-    <t>Total Amount (RM)</t>
-  </si>
-  <si>
     <t>Frequency per UOM</t>
   </si>
   <si>
@@ -42,13 +36,7 @@
     <t>No. UOM per month</t>
   </si>
   <si>
-    <t>No. UOM per year</t>
-  </si>
-  <si>
     <t>Price Type</t>
-  </si>
-  <si>
-    <t>Estimated  Value(RM)</t>
   </si>
   <si>
     <t>Specification</t>
@@ -419,19 +407,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -442,52 +430,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" customWidth="1"/>
     <col min="10" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
+++ b/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
@@ -4,19 +4,18 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="veryHidden" xWindow="0" yWindow="0" windowWidth="13545" windowHeight="4500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13545" windowHeight="4500"/>
   </bookViews>
   <sheets>
     <sheet name="ProductSheet" sheetId="1" r:id="rId1"/>
     <sheet name="ServiceSheet" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1:J6"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Item</t>
   </si>
@@ -42,7 +41,10 @@
     <t>Specification</t>
   </si>
   <si>
-    <t>Answer</t>
+    <t>Answer Remarks</t>
+  </si>
+  <si>
+    <t>Answer Text</t>
   </si>
 </sst>
 </file>
@@ -390,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
@@ -398,11 +400,11 @@
     <col min="3" max="3" width="6.28515625" customWidth="1"/>
     <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,6 +421,9 @@
         <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -430,7 +435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
@@ -440,12 +445,12 @@
     <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
     <col min="9" max="9" width="18.28515625" customWidth="1"/>
     <col min="10" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,9 +473,11 @@
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
   </sheetData>

--- a/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
+++ b/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4506"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13545" windowHeight="4500"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="14670" windowHeight="3180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ProductSheet" sheetId="1" r:id="rId1"/>
     <sheet name="ServiceSheet" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725"/>
+  <oleSize ref="A1:K9"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>Item</t>
   </si>
@@ -39,12 +40,6 @@
   </si>
   <si>
     <t>Specification</t>
-  </si>
-  <si>
-    <t>Answer Remarks</t>
-  </si>
-  <si>
-    <t>Answer Text</t>
   </si>
 </sst>
 </file>
@@ -420,12 +415,8 @@
       <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -472,12 +463,8 @@
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
     </row>
   </sheetData>

--- a/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
+++ b/portlets/NGeP-portlet/docroot/WEB-INF/templates/sc/loa/specification.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4506"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="14670" windowHeight="3180" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="14676" windowHeight="3180"/>
   </bookViews>
   <sheets>
     <sheet name="ProductSheet" sheetId="1" r:id="rId1"/>
     <sheet name="ServiceSheet" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <oleSize ref="A1:K9"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>Item</t>
   </si>
@@ -24,29 +23,26 @@
     <t>UOM</t>
   </si>
   <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Frequency per UOM</t>
-  </si>
-  <si>
-    <t>No. UOM per day</t>
-  </si>
-  <si>
-    <t>No. UOM per month</t>
-  </si>
-  <si>
-    <t>Price Type</t>
-  </si>
-  <si>
-    <t>Specification</t>
+    <t>Spesifikasi</t>
+  </si>
+  <si>
+    <t>Kekerapan / Unit Ukuran</t>
+  </si>
+  <si>
+    <t>Bil. Unit Ukuran Sehari</t>
+  </si>
+  <si>
+    <t>Bil. Unit Ukuran Sebulan</t>
+  </si>
+  <si>
+    <t>Jenis Harga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +173,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -211,6 +208,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -386,25 +384,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="6.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -412,9 +410,7 @@
       <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
@@ -425,28 +421,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" customWidth="1"/>
-    <col min="10" max="10" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -460,9 +456,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
